--- a/artfynd/A 63593-2025 artfynd.xlsx
+++ b/artfynd/A 63593-2025 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>115040446</v>
       </c>
       <c r="B2" t="n">
-        <v>57313</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57986</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -804,49 +799,44 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115040444</v>
+        <v>115040445</v>
       </c>
       <c r="B3" t="n">
-        <v>56674</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57903</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102952</v>
+        <v>102110</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tofsvipa</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Vanellus vanellus</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pontoppidan, 1763)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -891,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -901,7 +891,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Söder om rakan</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,49 +923,44 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115040445</v>
+        <v>115040444</v>
       </c>
       <c r="B4" t="n">
-        <v>57185</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57317</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102110</v>
+        <v>102952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Tofsvipa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Vanellus vanellus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -1015,7 +1005,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1025,12 +1015,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:24</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Söder om rakan</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 63593-2025 artfynd.xlsx
+++ b/artfynd/A 63593-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115040446</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -920,6 +930,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115040445</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1039,8 +1054,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115040444</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>